--- a/data/trans_dic/P2A_ner_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P2A_ner_R-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con problemas de nervios, depresión o trastorno mental</t>
+          <t>Hogares con personas con problemas de nervios, depresión o trastorno mental (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,75</t>
+          <t>0,0; 4,15</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,11; 9,96</t>
+          <t>1,11; 9,57</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,96; 8,5</t>
+          <t>0,98; 9,61</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,57; 7,8</t>
+          <t>1,65; 7,69</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,74</t>
+          <t>0,0; 5,26</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,47</t>
+          <t>0,0; 4,82</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,4; 12,36</t>
+          <t>2,48; 12,34</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,37; 5,92</t>
+          <t>0,36; 5,46</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,32; 3,35</t>
+          <t>0,32; 3,72</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,54; 5,34</t>
+          <t>0,53; 4,9</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,59; 9,02</t>
+          <t>2,49; 9,02</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,24; 5,0</t>
+          <t>1,21; 4,94</t>
         </is>
       </c>
     </row>
@@ -856,7 +857,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,97; 9,91</t>
+          <t>1,21; 9,25</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -866,52 +867,52 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,59; 9,69</t>
+          <t>1,44; 10,15</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,33; 8,08</t>
+          <t>1,29; 8,89</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,94; 7,98</t>
+          <t>0,93; 7,78</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,97</t>
+          <t>0,0; 5,96</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,78; 6,53</t>
+          <t>0,78; 6,84</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,02; 9,98</t>
+          <t>2,16; 10,47</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,61; 6,81</t>
+          <t>1,7; 6,72</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,47; 3,83</t>
+          <t>0,47; 3,89</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,59; 6,27</t>
+          <t>1,59; 6,6</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,33; 7,72</t>
+          <t>2,32; 7,61</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,18</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,07; 10,78</t>
+          <t>1,14; 9,91</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,22; 11,2</t>
+          <t>1,22; 9,99</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,27; 17,78</t>
+          <t>3,49; 17,76</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,8; 6,83</t>
+          <t>0,81; 7,59</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,75</t>
+          <t>0,0; 3,92</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,6</t>
+          <t>0,0; 6,55</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,75; 13,95</t>
+          <t>2,18; 14,42</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,47; 4,03</t>
+          <t>0,48; 4,46</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,05; 5,54</t>
+          <t>1,02; 5,95</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,13; 6,48</t>
+          <t>1,12; 6,29</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,86; 13,25</t>
+          <t>3,99; 12,71</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,27; 6,09</t>
+          <t>1,29; 5,85</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,5; 4,96</t>
+          <t>0,67; 5,24</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,22; 7,13</t>
+          <t>2,11; 7,35</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,58; 5,63</t>
+          <t>1,4; 5,72</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,45; 3,94</t>
+          <t>0,45; 3,84</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,64</t>
+          <t>0,0; 2,98</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,7; 8,03</t>
+          <t>2,51; 7,94</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,13; 8,1</t>
+          <t>3,13; 8,49</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,13; 4,1</t>
+          <t>1,14; 4,1</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,53; 2,98</t>
+          <t>0,59; 2,92</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,95; 6,46</t>
+          <t>2,93; 6,55</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,67; 5,94</t>
+          <t>2,64; 5,95</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,55</t>
+          <t>0,0; 4,15</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,35; 8,06</t>
+          <t>1,39; 8,39</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,64; 12,44</t>
+          <t>3,68; 12,5</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,31; 12,85</t>
+          <t>4,09; 12,01</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,27; 10,37</t>
+          <t>2,28; 11,36</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,68; 5,41</t>
+          <t>0,68; 5,96</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,02; 11,33</t>
+          <t>3,06; 11,89</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,6; 12,67</t>
+          <t>4,62; 12,11</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,65; 6,6</t>
+          <t>1,66; 6,63</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,43; 5,79</t>
+          <t>1,39; 5,57</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4,43; 10,51</t>
+          <t>4,18; 10,06</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,27; 10,74</t>
+          <t>5,32; 10,93</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,82; 7,59</t>
+          <t>0,82; 7,84</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,55</t>
+          <t>0,0; 10,07</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3,42; 14,74</t>
+          <t>2,45; 14,18</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4,46; 17,22</t>
+          <t>4,18; 17,01</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,88; 7,33</t>
+          <t>0,89; 7,86</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,57; 7,51</t>
+          <t>0,58; 7,01</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,02; 11,11</t>
+          <t>2,85; 12,3</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3,93; 17,03</t>
+          <t>4,07; 16,58</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,26; 5,75</t>
+          <t>1,33; 5,7</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,93; 5,67</t>
+          <t>0,88; 5,82</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3,42; 10,99</t>
+          <t>3,53; 11,08</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>5,51; 13,81</t>
+          <t>5,35; 14,0</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,27; 3,42</t>
+          <t>1,37; 3,35</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,93; 4,54</t>
+          <t>1,89; 4,58</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,69; 6,7</t>
+          <t>3,58; 6,68</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,89; 6,91</t>
+          <t>3,96; 6,9</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,76; 4,11</t>
+          <t>1,7; 4,04</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,7; 2,31</t>
+          <t>0,71; 2,42</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,49; 6,4</t>
+          <t>3,47; 6,38</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,16; 7,36</t>
+          <t>4,21; 7,4</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,77; 3,22</t>
+          <t>1,76; 3,33</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,47; 2,95</t>
+          <t>1,43; 2,93</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3,96; 6,06</t>
+          <t>3,91; 6,2</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>4,5; 6,49</t>
+          <t>4,44; 6,61</t>
         </is>
       </c>
     </row>
@@ -1638,4 +1639,1622 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Hogares con personas con problemas de nervios, depresión o trastorno mental (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>671</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2179</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2478</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>4052</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>1173</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>722</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>4700</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>2499</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>1843</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>2901</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>7178</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>6551</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3338</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>679; 5857</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>636; 6229</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>1729; 8034</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3770</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3542</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>1938; 9656</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>486; 7472</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>489; 5654</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>719; 6596</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>3566; 12911</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>2915; 11933</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>2665</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1264</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>3532</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>3682</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>2251</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>674</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2293</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>4875</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>4916</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>1938</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>5825</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>8557</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>834; 6355</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4428</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>1181; 8352</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>1225; 8418</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>629; 5250</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4084</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>729; 6364</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>2061; 10009</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>2317; 9153</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>629; 5212</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>2788; 11574</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>4407; 14470</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2928</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1849</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>4776</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>2173</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>648</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>1325</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>3934</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>2173</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>3575</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>3175</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>8710</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>757; 6592</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>600; 4916</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>1809; 9212</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>679; 6375</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2661</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3997</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>1394; 9206</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>680; 6344</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>1375; 8007</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>1230; 6929</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>4616; 14705</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>4518</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2709</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>6897</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>6858</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>2194</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>1486</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>8232</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>11504</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>6712</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>4195</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>15129</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>18362</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>1957; 8851</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>915; 7152</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>3504; 12189</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>3063; 12526</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>667; 5702</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4814</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>4282; 13575</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>6829; 18529</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>3411; 12292</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>1768; 8710</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>9868; 22044</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>11527; 25999</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>632</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>3575</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>7275</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>8953</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>4681</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>2047</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>6448</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>12832</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>5313</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>5622</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>13723</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>21784</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>0; 2870</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>1301; 7844</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>3734; 12693</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>4883; 14349</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>1926; 9607</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>628; 5482</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>3031; 11793</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>7517; 19693</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>2547; 10182</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>2582; 10338</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>8387; 20188</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>14991; 30838</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>2513</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>1531</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>4257</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>6088</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>1978</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>1823</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>4088</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>6522</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>4491</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>3354</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>8345</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>12610</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>612; 5872</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>0; 5429</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>1476; 8553</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>2882; 11718</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>644; 5689</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>429; 5190</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>1936; 8344</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>2930; 11938</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>1952; 8390</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>1121; 7447</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>4528; 14206</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>7536; 19721</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>11000</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>14185</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>26289</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>34409</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>14449</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>7400</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>27087</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>42165</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>25448</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>21585</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>53375</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>76574</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>6903; 16834</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>9022; 21847</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>18783; 35021</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>26080; 45440</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>8985; 21348</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>3828; 12996</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>19757; 36397</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>31508; 55416</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>18116; 34320</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>14470; 29724</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>42793; 67895</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>62481; 93003</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/P2A_ner_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P2A_ner_R-Clase-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,15</t>
+          <t>0,0; 4,17</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,11; 9,57</t>
+          <t>1,1; 9,53</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,98; 9,61</t>
+          <t>1,0; 9,22</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,65; 7,69</t>
+          <t>1,44; 8,01</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,26</t>
+          <t>0,0; 5,8</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,82</t>
+          <t>0,0; 4,89</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,48; 12,34</t>
+          <t>2,38; 12,1</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,36; 5,46</t>
+          <t>0,37; 5,21</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,32; 3,72</t>
+          <t>0,32; 3,26</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,53; 4,9</t>
+          <t>0,56; 5,4</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,49; 9,02</t>
+          <t>2,44; 8,79</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,21; 4,94</t>
+          <t>1,41; 5,15</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,21; 9,25</t>
+          <t>1,17; 9,79</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,77</t>
+          <t>0,0; 6,74</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,44; 10,15</t>
+          <t>1,4; 9,84</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,29; 8,89</t>
+          <t>1,24; 8,62</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,93; 7,78</t>
+          <t>0,94; 7,77</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,96</t>
+          <t>0,0; 5,89</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,78; 6,84</t>
+          <t>0,78; 6,83</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,16; 10,47</t>
+          <t>1,99; 9,79</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,7; 6,72</t>
+          <t>1,76; 7,17</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,47; 3,89</t>
+          <t>0,47; 4,24</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,59; 6,6</t>
+          <t>1,46; 6,44</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,32; 7,61</t>
+          <t>2,39; 7,87</t>
         </is>
       </c>
     </row>
@@ -1002,57 +1002,57 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,14; 9,91</t>
+          <t>1,15; 10,21</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,22; 9,99</t>
+          <t>1,21; 10,11</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,49; 17,76</t>
+          <t>4,24; 19,49</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,81; 7,59</t>
+          <t>0,81; 7,11</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,92</t>
+          <t>0,0; 5,36</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,55</t>
+          <t>0,0; 7,56</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,18; 14,42</t>
+          <t>1,98; 13,76</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,48; 4,46</t>
+          <t>0,47; 4,18</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,02; 5,95</t>
+          <t>1,01; 5,48</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,12; 6,29</t>
+          <t>1,12; 6,45</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,99; 12,71</t>
+          <t>3,89; 12,39</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,29; 5,85</t>
+          <t>1,27; 6,1</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,67; 5,24</t>
+          <t>0,49; 4,8</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,11; 7,35</t>
+          <t>2,24; 7,42</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,4; 5,72</t>
+          <t>1,61; 5,53</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,45; 3,84</t>
+          <t>0,45; 4,43</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,98</t>
+          <t>0,0; 2,86</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,51; 7,94</t>
+          <t>2,8; 8,09</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,13; 8,49</t>
+          <t>2,93; 8,47</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,14; 4,1</t>
+          <t>1,26; 4,05</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,59; 2,92</t>
+          <t>0,53; 3,08</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,93; 6,55</t>
+          <t>2,94; 6,71</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,64; 5,95</t>
+          <t>2,79; 6,02</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,15</t>
+          <t>0,0; 4,59</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,39; 8,39</t>
+          <t>1,36; 8,03</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,68; 12,5</t>
+          <t>3,86; 12,3</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,09; 12,01</t>
+          <t>4,23; 12,37</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,28; 11,36</t>
+          <t>2,26; 10,53</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,68; 5,96</t>
+          <t>0,67; 5,96</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,06; 11,89</t>
+          <t>3,09; 12,06</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,62; 12,11</t>
+          <t>4,75; 12,49</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,66; 6,63</t>
+          <t>1,38; 6,37</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,39; 5,57</t>
+          <t>1,25; 5,38</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4,18; 10,06</t>
+          <t>4,28; 9,96</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,32; 10,93</t>
+          <t>5,3; 11,1</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,82; 7,84</t>
+          <t>0,83; 8,41</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,07</t>
+          <t>0,0; 10,16</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,45; 14,18</t>
+          <t>2,41; 14,32</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4,18; 17,01</t>
+          <t>3,8; 16,12</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,89; 7,86</t>
+          <t>0,89; 7,33</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,58; 7,01</t>
+          <t>0,58; 6,67</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,85; 12,3</t>
+          <t>2,07; 11,4</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4,07; 16,58</t>
+          <t>4,59; 17,2</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,33; 5,7</t>
+          <t>1,3; 5,81</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,88; 5,82</t>
+          <t>0,94; 5,78</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3,53; 11,08</t>
+          <t>3,29; 10,55</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>5,35; 14,0</t>
+          <t>5,06; 13,84</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,37; 3,35</t>
+          <t>1,26; 3,38</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,89; 4,58</t>
+          <t>1,84; 4,62</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,58; 6,68</t>
+          <t>3,62; 6,73</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,96; 6,9</t>
+          <t>3,87; 6,74</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,7; 4,04</t>
+          <t>1,74; 3,9</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,71; 2,42</t>
+          <t>0,72; 2,48</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,47; 6,38</t>
+          <t>3,5; 6,53</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,21; 7,4</t>
+          <t>4,25; 7,21</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,76; 3,33</t>
+          <t>1,8; 3,32</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,43; 2,93</t>
+          <t>1,49; 2,93</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3,91; 6,2</t>
+          <t>3,97; 6,1</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>4,44; 6,61</t>
+          <t>4,47; 6,67</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3338</t>
+          <t>0; 3357</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>679; 5857</t>
+          <t>674; 5837</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>636; 6229</t>
+          <t>645; 5974</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1729; 8034</t>
+          <t>1504; 8365</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 3770</t>
+          <t>0; 4154</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 3542</t>
+          <t>0; 3590</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1938; 9656</t>
+          <t>1859; 9471</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>486; 7472</t>
+          <t>504; 7133</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>489; 5654</t>
+          <t>484; 4959</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>719; 6596</t>
+          <t>755; 7274</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3566; 12911</t>
+          <t>3489; 12584</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2915; 11933</t>
+          <t>3412; 12434</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>834; 6355</t>
+          <t>805; 6721</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 4428</t>
+          <t>0; 4405</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1181; 8352</t>
+          <t>1154; 8099</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1225; 8418</t>
+          <t>1179; 8157</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>629; 5250</t>
+          <t>636; 5243</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 4084</t>
+          <t>0; 4036</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>729; 6364</t>
+          <t>729; 6352</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2061; 10009</t>
+          <t>1905; 9353</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2317; 9153</t>
+          <t>2401; 9764</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>629; 5212</t>
+          <t>623; 5678</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2788; 11574</t>
+          <t>2569; 11295</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4407; 14470</t>
+          <t>4540; 14967</t>
         </is>
       </c>
     </row>
@@ -2348,57 +2348,57 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>757; 6592</t>
+          <t>762; 6792</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>600; 4916</t>
+          <t>595; 4977</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1809; 9212</t>
+          <t>2197; 10109</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>679; 6375</t>
+          <t>679; 5967</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 2661</t>
+          <t>0; 3641</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 3997</t>
+          <t>0; 4614</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1394; 9206</t>
+          <t>1262; 8789</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>680; 6344</t>
+          <t>672; 5942</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1375; 8007</t>
+          <t>1358; 7368</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1230; 6929</t>
+          <t>1230; 7114</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>4616; 14705</t>
+          <t>4498; 14334</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1957; 8851</t>
+          <t>1919; 9235</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>915; 7152</t>
+          <t>666; 6545</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3504; 12189</t>
+          <t>3722; 12295</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3063; 12526</t>
+          <t>3516; 12094</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>667; 5702</t>
+          <t>664; 6584</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 4814</t>
+          <t>0; 4622</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4282; 13575</t>
+          <t>4779; 13829</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6829; 18529</t>
+          <t>6405; 18478</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3411; 12292</t>
+          <t>3781; 12153</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1768; 8710</t>
+          <t>1575; 9185</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>9868; 22044</t>
+          <t>9895; 22585</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>11527; 25999</t>
+          <t>12178; 26321</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 2870</t>
+          <t>0; 3175</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1301; 7844</t>
+          <t>1275; 7508</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3734; 12693</t>
+          <t>3921; 12499</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4883; 14349</t>
+          <t>5048; 14778</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1926; 9607</t>
+          <t>1912; 8901</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>628; 5482</t>
+          <t>620; 5484</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3031; 11793</t>
+          <t>3061; 11961</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>7517; 19693</t>
+          <t>7722; 20309</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2547; 10182</t>
+          <t>2118; 9790</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2582; 10338</t>
+          <t>2315; 9974</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8387; 20188</t>
+          <t>8595; 19983</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>14991; 30838</t>
+          <t>14939; 31318</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>612; 5872</t>
+          <t>619; 6299</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 5429</t>
+          <t>0; 5476</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1476; 8553</t>
+          <t>1456; 8641</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2882; 11718</t>
+          <t>2621; 11106</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>644; 5689</t>
+          <t>642; 5309</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>429; 5190</t>
+          <t>426; 4937</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1936; 8344</t>
+          <t>1407; 7734</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2930; 11938</t>
+          <t>3306; 12384</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1952; 8390</t>
+          <t>1909; 8553</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1121; 7447</t>
+          <t>1206; 7395</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4528; 14206</t>
+          <t>4220; 13517</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>7536; 19721</t>
+          <t>7136; 19506</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>6903; 16834</t>
+          <t>6339; 16999</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>9022; 21847</t>
+          <t>8788; 22044</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>18783; 35021</t>
+          <t>18948; 35295</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>26080; 45440</t>
+          <t>25488; 44345</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>8985; 21348</t>
+          <t>9182; 20637</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3828; 12996</t>
+          <t>3877; 13310</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>19757; 36397</t>
+          <t>19943; 37205</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>31508; 55416</t>
+          <t>31876; 53998</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>18116; 34320</t>
+          <t>18550; 34230</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>14470; 29724</t>
+          <t>15145; 29718</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>42793; 67895</t>
+          <t>43441; 66799</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>62481; 93003</t>
+          <t>62877; 93879</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2A_ner_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P2A_ner_R-Clase-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1,64%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0,98%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>6,01%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2,18%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>0,83%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>3,56%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>3,82%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3,88%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1,64%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,98%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>6,01%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>3,13%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,17</t>
+          <t>0,0; 5,74</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,1; 9,53</t>
+          <t>0,0; 5,47</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,0; 9,22</t>
+          <t>2,4; 12,36</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,44; 8,01</t>
+          <t>0,36; 7,13</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,8</t>
+          <t>0,0; 4,75</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,89</t>
+          <t>1,11; 9,96</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,38; 12,1</t>
+          <t>0,96; 8,5</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,37; 5,21</t>
+          <t>1,71; 8,71</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,32; 3,26</t>
+          <t>0,32; 3,35</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,56; 5,4</t>
+          <t>0,54; 5,34</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,44; 8,79</t>
+          <t>2,59; 9,02</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,41; 5,15</t>
+          <t>1,45; 5,67</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>3,34%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0,98%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2,46%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>5,01%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>3,88%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>1,93%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>4,29%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>3,89%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>3,34%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0,98%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>2,46%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,46%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,17; 9,79</t>
+          <t>0,94; 7,98</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,74</t>
+          <t>0,0; 4,97</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,4; 9,84</t>
+          <t>0,78; 6,53</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,24; 8,62</t>
+          <t>1,91; 9,96</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,94; 7,77</t>
+          <t>0,97; 9,91</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,89</t>
+          <t>0,0; 6,77</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,78; 6,83</t>
+          <t>1,59; 9,69</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,99; 9,79</t>
+          <t>1,26; 8,18</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,76; 7,17</t>
+          <t>1,61; 6,81</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,47; 4,24</t>
+          <t>0,47; 3,83</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,46; 6,44</t>
+          <t>1,59; 6,27</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,39; 7,87</t>
+          <t>2,21; 7,81</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>2,59%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,95%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2,17%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>6,53%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>4,4%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>3,76%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>9,21%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>2,59%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0,95%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>2,17%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>8,36%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>0,8; 6,83</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 4,75</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 6,6</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>1,8; 15,3</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>1,15; 10,21</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>1,21; 10,11</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>4,24; 19,49</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>0,81; 7,11</t>
-        </is>
-      </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,36</t>
+          <t>1,07; 10,78</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,56</t>
+          <t>1,22; 11,2</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,98; 13,76</t>
+          <t>4,74; 19,7</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,47; 4,18</t>
+          <t>0,47; 4,03</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,01; 5,48</t>
+          <t>1,05; 5,54</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,12; 6,45</t>
+          <t>1,13; 6,48</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,89; 12,39</t>
+          <t>4,38; 14,54</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1,48%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0,92%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>4,82%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>5,58%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>2,99%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>1,98%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>4,16%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3,13%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1,48%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,92%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>4,82%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,68%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,27; 6,1</t>
+          <t>0,45; 3,94</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,49; 4,8</t>
+          <t>0,0; 3,64</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,24; 7,42</t>
+          <t>2,7; 8,03</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,61; 5,53</t>
+          <t>3,24; 8,79</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,45; 4,43</t>
+          <t>1,27; 6,09</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,86</t>
+          <t>0,5; 4,96</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,8; 8,09</t>
+          <t>2,22; 7,13</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,93; 8,47</t>
+          <t>1,95; 6,65</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,26; 4,05</t>
+          <t>1,13; 4,1</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,53; 3,08</t>
+          <t>0,53; 2,98</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,94; 6,71</t>
+          <t>2,95; 6,46</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,79; 6,02</t>
+          <t>2,99; 6,55</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>5,54%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>2,22%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>6,5%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>8,02%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>0,91%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>3,83%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>7,16%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>7,5%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>5,54%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>2,22%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>6,5%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,82%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,59</t>
+          <t>2,27; 10,37</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,36; 8,03</t>
+          <t>0,68; 5,41</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,86; 12,3</t>
+          <t>3,02; 11,33</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,23; 12,37</t>
+          <t>4,58; 13,05</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,26; 10,53</t>
+          <t>0,0; 5,55</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,67; 5,96</t>
+          <t>1,35; 8,06</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,09; 12,06</t>
+          <t>3,64; 12,44</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,75; 12,49</t>
+          <t>4,28; 13,19</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,38; 6,37</t>
+          <t>1,65; 6,6</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,25; 5,38</t>
+          <t>1,43; 5,79</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4,28; 9,96</t>
+          <t>4,43; 10,51</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,3; 11,1</t>
+          <t>5,25; 11,06</t>
         </is>
       </c>
     </row>
@@ -1349,42 +1349,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>2,73%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2,46%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>6,03%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>9,64%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>3,36%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>2,84%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>7,06%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>8,84%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>2,73%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>2,46%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>6,03%</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,22%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,83; 8,41</t>
+          <t>0,88; 7,33</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,16</t>
+          <t>0,57; 7,51</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,41; 14,32</t>
+          <t>2,02; 11,11</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,8; 16,12</t>
+          <t>4,12; 17,77</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,89; 7,33</t>
+          <t>0,82; 7,59</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,58; 6,67</t>
+          <t>0,0; 8,55</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,07; 11,4</t>
+          <t>3,42; 14,74</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4,59; 17,2</t>
+          <t>4,38; 17,31</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,3; 5,81</t>
+          <t>1,26; 5,75</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,94; 5,78</t>
+          <t>0,93; 5,67</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3,29; 10,55</t>
+          <t>3,42; 10,99</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>5,06; 13,84</t>
+          <t>5,66; 14,36</t>
         </is>
       </c>
     </row>
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>2,73%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1,38%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>4,75%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>5,9%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>2,19%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>2,97%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>5,02%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>5,23%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>2,73%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1,38%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>4,75%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,81%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,26; 3,38</t>
+          <t>1,76; 4,11</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,84; 4,62</t>
+          <t>0,7; 2,31</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,62; 6,73</t>
+          <t>3,49; 6,4</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,87; 6,74</t>
+          <t>4,3; 7,64</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,74; 3,9</t>
+          <t>1,27; 3,42</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,72; 2,48</t>
+          <t>1,93; 4,54</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,5; 6,53</t>
+          <t>3,69; 6,7</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,25; 7,21</t>
+          <t>4,3; 7,44</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,8; 3,32</t>
+          <t>1,77; 3,22</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,49; 2,93</t>
+          <t>1,47; 2,95</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3,97; 6,1</t>
+          <t>3,96; 6,06</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>4,47; 6,67</t>
+          <t>4,8; 6,91</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1683,7 +1683,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1791,42 +1791,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1859,42 +1859,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>1173</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>722</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>4700</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>2675</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>671</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>2179</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>2478</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>4052</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>1173</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>722</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>4700</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2499</t>
+          <t>4374</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>6551</t>
+          <t>7050</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3357</t>
+          <t>0; 4115</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>674; 5837</t>
+          <t>0; 4017</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>645; 5974</t>
+          <t>1879; 9672</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1504; 8365</t>
+          <t>436; 8735</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 4154</t>
+          <t>0; 3822</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 3590</t>
+          <t>682; 6099</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1859; 9471</t>
+          <t>623; 5511</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>504; 7133</t>
+          <t>1760; 8961</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>484; 4959</t>
+          <t>486; 5100</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>755; 7274</t>
+          <t>721; 7190</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3489; 12584</t>
+          <t>3700; 12913</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3412; 12434</t>
+          <t>3272; 12785</t>
         </is>
       </c>
     </row>
@@ -2004,37 +2004,37 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -2067,42 +2067,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>2251</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>674</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2293</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>4577</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>2665</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>1264</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>3532</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>3682</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>2251</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>674</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>2293</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>4875</t>
+          <t>3797</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>8557</t>
+          <t>8374</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>805; 6721</t>
+          <t>632; 5382</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 4405</t>
+          <t>0; 3407</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1154; 8099</t>
+          <t>727; 6078</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1179; 8157</t>
+          <t>1747; 9104</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>636; 5243</t>
+          <t>663; 6804</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 4036</t>
+          <t>0; 4423</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>729; 6352</t>
+          <t>1305; 7974</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1905; 9353</t>
+          <t>1213; 7900</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2401; 9764</t>
+          <t>2186; 9279</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>623; 5678</t>
+          <t>623; 5123</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2569; 11295</t>
+          <t>2785; 10989</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4540; 14967</t>
+          <t>4160; 14684</t>
         </is>
       </c>
     </row>
@@ -2207,42 +2207,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2275,49 +2275,49 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>2173</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>648</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1325</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>3716</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>2928</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>1849</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>4776</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>5512</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>2173</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>648</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>1325</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>3934</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>2173</t>
-        </is>
-      </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
           <t>3575</t>
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>8710</t>
+          <t>9228</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>672; 5736</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3230</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4027</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>1024; 8710</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>762; 6792</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>595; 4977</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>2197; 10109</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>679; 5967</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 3641</t>
+          <t>714; 7170</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 4614</t>
+          <t>601; 5516</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1262; 8789</t>
+          <t>2537; 10535</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>672; 5942</t>
+          <t>674; 5727</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1358; 7368</t>
+          <t>1406; 7451</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1230; 7114</t>
+          <t>1243; 7143</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>4498; 14334</t>
+          <t>4834; 16058</t>
         </is>
       </c>
     </row>
@@ -2415,42 +2415,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>11</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2483,42 +2483,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>2194</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1486</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>8232</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>11271</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>4518</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>2709</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>6897</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>6858</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>2194</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>1486</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>8232</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>11504</t>
+          <t>6595</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>18362</t>
+          <t>17866</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1919; 9235</t>
+          <t>666; 5855</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>666; 6545</t>
+          <t>0; 5874</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3722; 12295</t>
+          <t>4608; 13726</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3516; 12094</t>
+          <t>6549; 17760</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>664; 6584</t>
+          <t>1926; 9219</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 4622</t>
+          <t>678; 6768</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4779; 13829</t>
+          <t>3687; 11816</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6405; 18478</t>
+          <t>3502; 11954</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3781; 12153</t>
+          <t>3381; 12282</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1575; 9185</t>
+          <t>1572; 8864</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>9895; 22585</t>
+          <t>9916; 21750</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>12178; 26321</t>
+          <t>11404; 24985</t>
         </is>
       </c>
     </row>
@@ -2623,42 +2623,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>14</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2691,42 +2691,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>4681</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>2047</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>6448</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>11886</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>632</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>3575</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>7275</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>8953</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>4681</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>2047</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>6448</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>12832</t>
+          <t>8989</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>21784</t>
+          <t>20875</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 3175</t>
+          <t>1920; 8764</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1275; 7508</t>
+          <t>624; 4980</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3921; 12499</t>
+          <t>2994; 11236</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5048; 14778</t>
+          <t>6794; 19339</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1912; 8901</t>
+          <t>0; 3837</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>620; 5484</t>
+          <t>1261; 7531</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3061; 11961</t>
+          <t>3696; 12637</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>7722; 20309</t>
+          <t>5082; 15655</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2118; 9790</t>
+          <t>2542; 10144</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2315; 9974</t>
+          <t>2644; 10734</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8595; 19983</t>
+          <t>8901; 21106</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>14939; 31318</t>
+          <t>14027; 29533</t>
         </is>
       </c>
     </row>
@@ -2831,42 +2831,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -2899,42 +2899,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>1978</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>1823</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>4088</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>6580</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>2513</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>1531</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>4257</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>6088</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>1978</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>1823</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>4088</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>6522</t>
+          <t>6200</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>12610</t>
+          <t>12780</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>619; 6299</t>
+          <t>636; 5309</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 5476</t>
+          <t>424; 5561</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1456; 8641</t>
+          <t>1373; 7536</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2621; 11106</t>
+          <t>2812; 12136</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>642; 5309</t>
+          <t>615; 5681</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>426; 4937</t>
+          <t>0; 4608</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1407; 7734</t>
+          <t>2064; 8895</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>3306; 12384</t>
+          <t>3078; 12180</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1909; 8553</t>
+          <t>1857; 8463</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1206; 7395</t>
+          <t>1187; 7255</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4220; 13517</t>
+          <t>4381; 14090</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>7136; 19506</t>
+          <t>7847; 19914</t>
         </is>
       </c>
     </row>
@@ -3039,42 +3039,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>53</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3107,42 +3107,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>14449</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>7400</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>27087</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>40704</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>11000</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>14185</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>26289</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>34409</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>14449</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>7400</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>27087</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>42165</t>
+          <t>35468</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>76574</t>
+          <t>76172</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>6339; 16999</t>
+          <t>9318; 21718</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>8788; 22044</t>
+          <t>3754; 12389</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>18948; 35295</t>
+          <t>19902; 36499</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>25488; 44345</t>
+          <t>29662; 52674</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>9182; 20637</t>
+          <t>6365; 17200</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3877; 13310</t>
+          <t>9196; 21670</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>19943; 37205</t>
+          <t>19336; 35136</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>31876; 53998</t>
+          <t>26750; 46250</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>18550; 34230</t>
+          <t>18280; 33182</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>15145; 29718</t>
+          <t>14873; 29938</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>43441; 66799</t>
+          <t>43306; 66284</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>62877; 93879</t>
+          <t>62923; 90535</t>
         </is>
       </c>
     </row>
